--- a/output/yearly_population_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_29_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8141</v>
+        <v>6664</v>
       </c>
       <c r="C2" t="n">
-        <v>4838</v>
+        <v>8002</v>
       </c>
       <c r="D2" t="n">
-        <v>21489</v>
+        <v>23376</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4655</v>
+        <v>3894</v>
       </c>
       <c r="C3" t="n">
-        <v>4890</v>
+        <v>5555</v>
       </c>
       <c r="D3" t="n">
-        <v>15249</v>
+        <v>12276</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3342</v>
+        <v>3086</v>
       </c>
       <c r="C4" t="n">
-        <v>6053</v>
+        <v>3203</v>
       </c>
       <c r="D4" t="n">
-        <v>7690</v>
+        <v>6345</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2218</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>5280</v>
+        <v>2176</v>
       </c>
       <c r="D5" t="n">
-        <v>3005</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>1198</v>
       </c>
       <c r="C6" t="n">
-        <v>3244</v>
+        <v>1462</v>
       </c>
       <c r="D6" t="n">
-        <v>1211</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>635</v>
+        <v>575</v>
       </c>
       <c r="C7" t="n">
-        <v>1603</v>
+        <v>876</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="C8" t="n">
-        <v>718</v>
+        <v>491</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8117</v>
+        <v>10255</v>
       </c>
       <c r="C2" t="n">
-        <v>3719</v>
+        <v>6728</v>
       </c>
       <c r="D2" t="n">
-        <v>27016</v>
+        <v>19415</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5010</v>
+        <v>4223</v>
       </c>
       <c r="C3" t="n">
-        <v>4290</v>
+        <v>5909</v>
       </c>
       <c r="D3" t="n">
-        <v>15072</v>
+        <v>13029</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3362</v>
+        <v>2965</v>
       </c>
       <c r="C4" t="n">
-        <v>5380</v>
+        <v>4324</v>
       </c>
       <c r="D4" t="n">
-        <v>8689</v>
+        <v>7116</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2381</v>
+        <v>2242</v>
       </c>
       <c r="C5" t="n">
-        <v>5468</v>
+        <v>2653</v>
       </c>
       <c r="D5" t="n">
-        <v>3604</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1542</v>
+        <v>1438</v>
       </c>
       <c r="C6" t="n">
-        <v>4111</v>
+        <v>1781</v>
       </c>
       <c r="D6" t="n">
-        <v>1470</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>829</v>
+        <v>772</v>
       </c>
       <c r="C7" t="n">
-        <v>2294</v>
+        <v>1162</v>
       </c>
       <c r="D7" t="n">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>671</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
+        <v>241</v>
+      </c>
+      <c r="D10" t="n">
         <v>249</v>
-      </c>
-      <c r="D10" t="n">
-        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9197</v>
+        <v>10833</v>
       </c>
       <c r="C2" t="n">
-        <v>10132</v>
+        <v>6821</v>
       </c>
       <c r="D2" t="n">
-        <v>34593</v>
+        <v>33153</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5091</v>
+        <v>5532</v>
       </c>
       <c r="C3" t="n">
-        <v>3615</v>
+        <v>5527</v>
       </c>
       <c r="D3" t="n">
-        <v>15540</v>
+        <v>13021</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3412</v>
+        <v>3001</v>
       </c>
       <c r="C4" t="n">
-        <v>4756</v>
+        <v>4953</v>
       </c>
       <c r="D4" t="n">
-        <v>9260</v>
+        <v>7796</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2461</v>
+        <v>2299</v>
       </c>
       <c r="C5" t="n">
-        <v>5265</v>
+        <v>3383</v>
       </c>
       <c r="D5" t="n">
-        <v>4226</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1724</v>
+        <v>1631</v>
       </c>
       <c r="C6" t="n">
-        <v>4621</v>
+        <v>2139</v>
       </c>
       <c r="D6" t="n">
-        <v>1723</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>991</v>
+        <v>954</v>
       </c>
       <c r="C7" t="n">
-        <v>2982</v>
+        <v>1440</v>
       </c>
       <c r="D7" t="n">
-        <v>817</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C8" t="n">
-        <v>1539</v>
+        <v>875</v>
       </c>
       <c r="D8" t="n">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C9" t="n">
-        <v>703</v>
+        <v>498</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>325</v>
+        <v>291</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8497</v>
+        <v>9671</v>
       </c>
       <c r="C2" t="n">
-        <v>6970</v>
+        <v>4365</v>
       </c>
       <c r="D2" t="n">
-        <v>28420</v>
+        <v>26366</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6116</v>
+        <v>6280</v>
       </c>
       <c r="C3" t="n">
-        <v>6614</v>
+        <v>8204</v>
       </c>
       <c r="D3" t="n">
-        <v>17017</v>
+        <v>14900</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2273</v>
+        <v>2124</v>
       </c>
       <c r="C4" t="n">
-        <v>7611</v>
+        <v>6195</v>
       </c>
       <c r="D4" t="n">
-        <v>8965</v>
+        <v>7676</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1592</v>
+        <v>1507</v>
       </c>
       <c r="C5" t="n">
-        <v>4528</v>
+        <v>2096</v>
       </c>
       <c r="D5" t="n">
-        <v>2824</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>915</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>2922</v>
+        <v>1411</v>
       </c>
       <c r="D6" t="n">
-        <v>800</v>
+        <v>787</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>1508</v>
+        <v>857</v>
       </c>
       <c r="D7" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>688</v>
+        <v>488</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5212</v>
+        <v>5675</v>
       </c>
       <c r="C2" t="n">
-        <v>3966</v>
+        <v>2416</v>
       </c>
       <c r="D2" t="n">
-        <v>20913</v>
+        <v>17974</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6158</v>
+        <v>6775</v>
       </c>
       <c r="C3" t="n">
-        <v>6145</v>
+        <v>5701</v>
       </c>
       <c r="D3" t="n">
-        <v>17750</v>
+        <v>15669</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3224</v>
+        <v>3282</v>
       </c>
       <c r="C4" t="n">
-        <v>7285</v>
+        <v>7247</v>
       </c>
       <c r="D4" t="n">
-        <v>9938</v>
+        <v>8768</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1763</v>
+        <v>1676</v>
       </c>
       <c r="C5" t="n">
-        <v>5850</v>
+        <v>4002</v>
       </c>
       <c r="D5" t="n">
-        <v>3558</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1084</v>
+        <v>1052</v>
       </c>
       <c r="C6" t="n">
-        <v>3655</v>
+        <v>1758</v>
       </c>
       <c r="D6" t="n">
-        <v>1008</v>
+        <v>987</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>1999</v>
+        <v>1100</v>
       </c>
       <c r="D7" t="n">
         <v>523</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C8" t="n">
-        <v>930</v>
+        <v>623</v>
       </c>
       <c r="D8" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5307</v>
+        <v>6258</v>
       </c>
       <c r="C2" t="n">
-        <v>10283</v>
+        <v>4778</v>
       </c>
       <c r="D2" t="n">
-        <v>28412</v>
+        <v>17777</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4846</v>
+        <v>5263</v>
       </c>
       <c r="C3" t="n">
-        <v>4508</v>
+        <v>3545</v>
       </c>
       <c r="D3" t="n">
-        <v>16987</v>
+        <v>14916</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3826</v>
+        <v>4219</v>
       </c>
       <c r="C4" t="n">
-        <v>6575</v>
+        <v>6279</v>
       </c>
       <c r="D4" t="n">
-        <v>10910</v>
+        <v>9760</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="C5" t="n">
-        <v>6459</v>
+        <v>5608</v>
       </c>
       <c r="D5" t="n">
-        <v>4429</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1267</v>
+        <v>1226</v>
       </c>
       <c r="C6" t="n">
-        <v>4589</v>
+        <v>2816</v>
       </c>
       <c r="D6" t="n">
-        <v>1361</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>586</v>
+        <v>620</v>
       </c>
       <c r="C7" t="n">
-        <v>2731</v>
+        <v>1419</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C8" t="n">
-        <v>1368</v>
+        <v>839</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>469</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3229</v>
+        <v>3619</v>
       </c>
       <c r="C2" t="n">
-        <v>4816</v>
+        <v>2086</v>
       </c>
       <c r="D2" t="n">
-        <v>19802</v>
+        <v>12146</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4780</v>
+        <v>5323</v>
       </c>
       <c r="C3" t="n">
-        <v>6311</v>
+        <v>3868</v>
       </c>
       <c r="D3" t="n">
-        <v>17794</v>
+        <v>14877</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4206</v>
+        <v>4689</v>
       </c>
       <c r="C4" t="n">
-        <v>6457</v>
+        <v>5753</v>
       </c>
       <c r="D4" t="n">
-        <v>11669</v>
+        <v>10476</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2198</v>
+        <v>2225</v>
       </c>
       <c r="C5" t="n">
-        <v>7485</v>
+        <v>6521</v>
       </c>
       <c r="D5" t="n">
-        <v>4670</v>
+        <v>4512</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1056</v>
+        <v>1105</v>
       </c>
       <c r="C6" t="n">
-        <v>5420</v>
+        <v>3592</v>
       </c>
       <c r="D6" t="n">
-        <v>1330</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>2718</v>
+        <v>1521</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>980</v>
+        <v>747</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4719</v>
+        <v>6305</v>
       </c>
       <c r="C2" t="n">
-        <v>8134</v>
+        <v>2130</v>
       </c>
       <c r="D2" t="n">
-        <v>16755</v>
+        <v>10886</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3543</v>
+        <v>3904</v>
       </c>
       <c r="C3" t="n">
-        <v>5016</v>
+        <v>2646</v>
       </c>
       <c r="D3" t="n">
-        <v>17042</v>
+        <v>13460</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3917</v>
+        <v>4341</v>
       </c>
       <c r="C4" t="n">
-        <v>6316</v>
+        <v>4729</v>
       </c>
       <c r="D4" t="n">
-        <v>12255</v>
+        <v>10918</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2655</v>
+        <v>2894</v>
       </c>
       <c r="C5" t="n">
-        <v>6947</v>
+        <v>6079</v>
       </c>
       <c r="D5" t="n">
-        <v>5535</v>
+        <v>5391</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1341</v>
+        <v>1434</v>
       </c>
       <c r="C6" t="n">
-        <v>6276</v>
+        <v>4913</v>
       </c>
       <c r="D6" t="n">
-        <v>1761</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="C7" t="n">
-        <v>3802</v>
+        <v>2443</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1638</v>
+        <v>1064</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
         <v>101</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3319</v>
+        <v>4281</v>
       </c>
       <c r="C2" t="n">
-        <v>4481</v>
+        <v>2430</v>
       </c>
       <c r="D2" t="n">
-        <v>12263</v>
+        <v>8143</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3434</v>
+        <v>4162</v>
       </c>
       <c r="C3" t="n">
-        <v>5656</v>
+        <v>2206</v>
       </c>
       <c r="D3" t="n">
-        <v>16080</v>
+        <v>12376</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3508</v>
+        <v>3867</v>
       </c>
       <c r="C4" t="n">
-        <v>5842</v>
+        <v>3801</v>
       </c>
       <c r="D4" t="n">
-        <v>12761</v>
+        <v>11056</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2893</v>
+        <v>3207</v>
       </c>
       <c r="C5" t="n">
-        <v>6845</v>
+        <v>5641</v>
       </c>
       <c r="D5" t="n">
-        <v>6129</v>
+        <v>6020</v>
       </c>
     </row>
     <row r="6">
@@ -3324,10 +3324,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1563</v>
+        <v>1720</v>
       </c>
       <c r="C6" t="n">
-        <v>6741</v>
+        <v>5519</v>
       </c>
       <c r="D6" t="n">
         <v>2117</v>
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>469</v>
       </c>
       <c r="C7" t="n">
-        <v>4605</v>
+        <v>3311</v>
       </c>
       <c r="D7" t="n">
-        <v>753</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>2161</v>
+        <v>1442</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4985</v>
+        <v>6125</v>
       </c>
       <c r="C2" t="n">
-        <v>3343</v>
+        <v>6099</v>
       </c>
       <c r="D2" t="n">
-        <v>23880</v>
+        <v>8176</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2857</v>
+        <v>3532</v>
       </c>
       <c r="C3" t="n">
-        <v>4617</v>
+        <v>2053</v>
       </c>
       <c r="D3" t="n">
-        <v>14592</v>
+        <v>11087</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026</v>
+        <v>3458</v>
       </c>
       <c r="C4" t="n">
-        <v>5641</v>
+        <v>2986</v>
       </c>
       <c r="D4" t="n">
-        <v>12851</v>
+        <v>10922</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2830</v>
+        <v>3174</v>
       </c>
       <c r="C5" t="n">
-        <v>6298</v>
+        <v>4711</v>
       </c>
       <c r="D5" t="n">
-        <v>6834</v>
+        <v>6504</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1868</v>
+        <v>2104</v>
       </c>
       <c r="C6" t="n">
-        <v>6724</v>
+        <v>5519</v>
       </c>
       <c r="D6" t="n">
-        <v>2590</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>653</v>
+        <v>804</v>
       </c>
       <c r="C7" t="n">
-        <v>5443</v>
+        <v>4250</v>
       </c>
       <c r="D7" t="n">
-        <v>905</v>
+        <v>972</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>2998</v>
+        <v>2155</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C9" t="n">
-        <v>1089</v>
+        <v>881</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9506</v>
+        <v>6543</v>
       </c>
       <c r="C2" t="n">
-        <v>5489</v>
+        <v>3201</v>
       </c>
       <c r="D2" t="n">
-        <v>12609</v>
+        <v>5763</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3607</v>
+        <v>4243</v>
       </c>
       <c r="C2" t="n">
-        <v>1925</v>
+        <v>3269</v>
       </c>
       <c r="D2" t="n">
-        <v>17767</v>
+        <v>5952</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3812</v>
+        <v>4696</v>
       </c>
       <c r="C3" t="n">
-        <v>4737</v>
+        <v>3285</v>
       </c>
       <c r="D3" t="n">
-        <v>16209</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4161</v>
+        <v>4701</v>
       </c>
       <c r="C4" t="n">
-        <v>7853</v>
+        <v>4428</v>
       </c>
       <c r="D4" t="n">
-        <v>13113</v>
+        <v>11292</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1778</v>
+        <v>2120</v>
       </c>
       <c r="C5" t="n">
-        <v>9388</v>
+        <v>7366</v>
       </c>
       <c r="D5" t="n">
-        <v>6189</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>603</v>
+        <v>742</v>
       </c>
       <c r="C6" t="n">
-        <v>6586</v>
+        <v>5463</v>
       </c>
       <c r="D6" t="n">
-        <v>2040</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>2938</v>
+        <v>2111</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>1067</v>
+        <v>863</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8722</v>
+        <v>6513</v>
       </c>
       <c r="C2" t="n">
-        <v>4201</v>
+        <v>2327</v>
       </c>
       <c r="D2" t="n">
-        <v>14089</v>
+        <v>12936</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4036</v>
+        <v>2779</v>
       </c>
       <c r="C3" t="n">
-        <v>2766</v>
+        <v>1638</v>
       </c>
       <c r="D3" t="n">
-        <v>2757</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5308</v>
+        <v>5638</v>
       </c>
       <c r="C2" t="n">
-        <v>8470</v>
+        <v>2772</v>
       </c>
       <c r="D2" t="n">
-        <v>28265</v>
+        <v>17014</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5243</v>
+        <v>3869</v>
       </c>
       <c r="C3" t="n">
-        <v>3085</v>
+        <v>1751</v>
       </c>
       <c r="D3" t="n">
-        <v>4457</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1788</v>
+        <v>1241</v>
       </c>
       <c r="C4" t="n">
-        <v>1665</v>
+        <v>1018</v>
       </c>
       <c r="D4" t="n">
-        <v>1736</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>98</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5395</v>
+        <v>5472</v>
       </c>
       <c r="C2" t="n">
-        <v>6465</v>
+        <v>2928</v>
       </c>
       <c r="D2" t="n">
-        <v>26691</v>
+        <v>20877</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4358</v>
+        <v>3903</v>
       </c>
       <c r="C3" t="n">
-        <v>5212</v>
+        <v>2002</v>
       </c>
       <c r="D3" t="n">
-        <v>7945</v>
+        <v>5353</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2996</v>
+        <v>2198</v>
       </c>
       <c r="C4" t="n">
-        <v>2434</v>
+        <v>1419</v>
       </c>
       <c r="D4" t="n">
-        <v>2205</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>778</v>
+        <v>568</v>
       </c>
       <c r="C5" t="n">
-        <v>1005</v>
+        <v>659</v>
       </c>
       <c r="D5" t="n">
-        <v>1248</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7873</v>
+        <v>5962</v>
       </c>
       <c r="C2" t="n">
-        <v>12388</v>
+        <v>3933</v>
       </c>
       <c r="D2" t="n">
-        <v>28154</v>
+        <v>24950</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3990</v>
+        <v>3830</v>
       </c>
       <c r="C3" t="n">
-        <v>5097</v>
+        <v>2161</v>
       </c>
       <c r="D3" t="n">
-        <v>10235</v>
+        <v>7335</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3111</v>
+        <v>2607</v>
       </c>
       <c r="C4" t="n">
-        <v>3876</v>
+        <v>1694</v>
       </c>
       <c r="D4" t="n">
-        <v>3184</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1558</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>1724</v>
+        <v>1053</v>
       </c>
       <c r="D5" t="n">
-        <v>1363</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>388</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>647</v>
+        <v>484</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>79</v>
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7605</v>
+        <v>6573</v>
       </c>
       <c r="C2" t="n">
-        <v>9015</v>
+        <v>3991</v>
       </c>
       <c r="D2" t="n">
-        <v>25608</v>
+        <v>23352</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4257</v>
+        <v>3577</v>
       </c>
       <c r="C3" t="n">
-        <v>7173</v>
+        <v>2537</v>
       </c>
       <c r="D3" t="n">
-        <v>11513</v>
+        <v>9066</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2209</v>
+        <v>2023</v>
       </c>
       <c r="C4" t="n">
-        <v>3682</v>
+        <v>1609</v>
       </c>
       <c r="D4" t="n">
-        <v>3817</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1216</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>2077</v>
+        <v>1015</v>
       </c>
       <c r="D5" t="n">
-        <v>1314</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>354</v>
       </c>
       <c r="C6" t="n">
-        <v>790</v>
+        <v>527</v>
       </c>
       <c r="D6" t="n">
-        <v>779</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>318</v>
+        <v>268</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6523</v>
+        <v>5920</v>
       </c>
       <c r="C2" t="n">
-        <v>7062</v>
+        <v>5622</v>
       </c>
       <c r="D2" t="n">
-        <v>28920</v>
+        <v>19575</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4904</v>
+        <v>4263</v>
       </c>
       <c r="C3" t="n">
-        <v>7091</v>
+        <v>2935</v>
       </c>
       <c r="D3" t="n">
-        <v>13033</v>
+        <v>10898</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2808</v>
+        <v>2486</v>
       </c>
       <c r="C4" t="n">
-        <v>5716</v>
+        <v>2163</v>
       </c>
       <c r="D4" t="n">
-        <v>5215</v>
+        <v>4052</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1532</v>
+        <v>1350</v>
       </c>
       <c r="C5" t="n">
-        <v>2973</v>
+        <v>1358</v>
       </c>
       <c r="D5" t="n">
-        <v>1778</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>773</v>
+        <v>637</v>
       </c>
       <c r="C6" t="n">
-        <v>1509</v>
+        <v>810</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="C7" t="n">
-        <v>581</v>
+        <v>420</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6886</v>
+        <v>5274</v>
       </c>
       <c r="C2" t="n">
-        <v>5005</v>
+        <v>8474</v>
       </c>
       <c r="D2" t="n">
-        <v>25889</v>
+        <v>21273</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4677</v>
+        <v>4206</v>
       </c>
       <c r="C3" t="n">
-        <v>6135</v>
+        <v>3859</v>
       </c>
       <c r="D3" t="n">
-        <v>14636</v>
+        <v>11553</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3273</v>
+        <v>2947</v>
       </c>
       <c r="C4" t="n">
-        <v>6362</v>
+        <v>2556</v>
       </c>
       <c r="D4" t="n">
-        <v>6557</v>
+        <v>5308</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1902</v>
+        <v>1695</v>
       </c>
       <c r="C5" t="n">
-        <v>4385</v>
+        <v>1801</v>
       </c>
       <c r="D5" t="n">
-        <v>2350</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1036</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>2236</v>
+        <v>1110</v>
       </c>
       <c r="D6" t="n">
-        <v>1006</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>449</v>
+        <v>381</v>
       </c>
       <c r="C7" t="n">
-        <v>1062</v>
+        <v>637</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C8" t="n">
-        <v>426</v>
+        <v>340</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_29_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6664</v>
+        <v>4747</v>
       </c>
       <c r="C2" t="n">
-        <v>8002</v>
+        <v>5298</v>
       </c>
       <c r="D2" t="n">
-        <v>23376</v>
+        <v>35336</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3894</v>
+        <v>2976</v>
       </c>
       <c r="C3" t="n">
-        <v>5555</v>
+        <v>5862</v>
       </c>
       <c r="D3" t="n">
-        <v>12276</v>
+        <v>17708</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3086</v>
+        <v>2505</v>
       </c>
       <c r="C4" t="n">
-        <v>3203</v>
+        <v>6526</v>
       </c>
       <c r="D4" t="n">
-        <v>6345</v>
+        <v>9121</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2025</v>
+        <v>1593</v>
       </c>
       <c r="C5" t="n">
-        <v>2176</v>
+        <v>5327</v>
       </c>
       <c r="D5" t="n">
-        <v>2464</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1198</v>
+        <v>908</v>
       </c>
       <c r="C6" t="n">
-        <v>1462</v>
+        <v>3513</v>
       </c>
       <c r="D6" t="n">
-        <v>1108</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>575</v>
+        <v>409</v>
       </c>
       <c r="C7" t="n">
-        <v>876</v>
+        <v>2081</v>
       </c>
       <c r="D7" t="n">
-        <v>651</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>491</v>
+        <v>1001</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>283</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10255</v>
+        <v>5305</v>
       </c>
       <c r="C2" t="n">
-        <v>6728</v>
+        <v>7772</v>
       </c>
       <c r="D2" t="n">
-        <v>19415</v>
+        <v>28776</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4223</v>
+        <v>3040</v>
       </c>
       <c r="C3" t="n">
-        <v>5909</v>
+        <v>4960</v>
       </c>
       <c r="D3" t="n">
-        <v>13029</v>
+        <v>18802</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2965</v>
+        <v>2337</v>
       </c>
       <c r="C4" t="n">
-        <v>4324</v>
+        <v>6084</v>
       </c>
       <c r="D4" t="n">
-        <v>7116</v>
+        <v>10075</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2242</v>
+        <v>1738</v>
       </c>
       <c r="C5" t="n">
-        <v>2653</v>
+        <v>5694</v>
       </c>
       <c r="D5" t="n">
-        <v>3059</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1438</v>
+        <v>1081</v>
       </c>
       <c r="C6" t="n">
-        <v>1781</v>
+        <v>4263</v>
       </c>
       <c r="D6" t="n">
-        <v>1303</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>772</v>
+        <v>547</v>
       </c>
       <c r="C7" t="n">
-        <v>1162</v>
+        <v>2663</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338</v>
+        <v>226</v>
       </c>
       <c r="C8" t="n">
-        <v>671</v>
+        <v>1445</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>639</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10833</v>
+        <v>6012</v>
       </c>
       <c r="C2" t="n">
-        <v>6821</v>
+        <v>7834</v>
       </c>
       <c r="D2" t="n">
-        <v>33153</v>
+        <v>24240</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5532</v>
+        <v>3185</v>
       </c>
       <c r="C3" t="n">
-        <v>5527</v>
+        <v>5387</v>
       </c>
       <c r="D3" t="n">
-        <v>13021</v>
+        <v>18795</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3001</v>
+        <v>2226</v>
       </c>
       <c r="C4" t="n">
-        <v>4953</v>
+        <v>5435</v>
       </c>
       <c r="D4" t="n">
-        <v>7796</v>
+        <v>11025</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2299</v>
+        <v>1756</v>
       </c>
       <c r="C5" t="n">
-        <v>3383</v>
+        <v>5678</v>
       </c>
       <c r="D5" t="n">
-        <v>3628</v>
+        <v>4741</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1631</v>
+        <v>1215</v>
       </c>
       <c r="C6" t="n">
-        <v>2139</v>
+        <v>4789</v>
       </c>
       <c r="D6" t="n">
-        <v>1542</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>954</v>
+        <v>673</v>
       </c>
       <c r="C7" t="n">
-        <v>1440</v>
+        <v>3247</v>
       </c>
       <c r="D7" t="n">
-        <v>804</v>
+        <v>831</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>466</v>
+        <v>307</v>
       </c>
       <c r="C8" t="n">
-        <v>875</v>
+        <v>1883</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>118</v>
       </c>
       <c r="C9" t="n">
-        <v>498</v>
+        <v>924</v>
       </c>
       <c r="D9" t="n">
-        <v>345</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>291</v>
+        <v>414</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9671</v>
+        <v>5548</v>
       </c>
       <c r="C2" t="n">
-        <v>4365</v>
+        <v>5452</v>
       </c>
       <c r="D2" t="n">
-        <v>26366</v>
+        <v>20294</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6280</v>
+        <v>3877</v>
       </c>
       <c r="C3" t="n">
-        <v>8204</v>
+        <v>8282</v>
       </c>
       <c r="D3" t="n">
-        <v>14900</v>
+        <v>20527</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2124</v>
+        <v>1622</v>
       </c>
       <c r="C4" t="n">
-        <v>6195</v>
+        <v>8372</v>
       </c>
       <c r="D4" t="n">
-        <v>7676</v>
+        <v>10474</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1507</v>
+        <v>1122</v>
       </c>
       <c r="C5" t="n">
-        <v>2096</v>
+        <v>4693</v>
       </c>
       <c r="D5" t="n">
-        <v>2556</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>621</v>
       </c>
       <c r="C6" t="n">
-        <v>1411</v>
+        <v>3182</v>
       </c>
       <c r="D6" t="n">
-        <v>787</v>
+        <v>814</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>857</v>
+        <v>1845</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>488</v>
+        <v>905</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>285</v>
+        <v>405</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5675</v>
+        <v>3370</v>
       </c>
       <c r="C2" t="n">
-        <v>2416</v>
+        <v>2676</v>
       </c>
       <c r="D2" t="n">
-        <v>17974</v>
+        <v>14451</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6775</v>
+        <v>3944</v>
       </c>
       <c r="C3" t="n">
-        <v>5701</v>
+        <v>6394</v>
       </c>
       <c r="D3" t="n">
-        <v>15669</v>
+        <v>19510</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3282</v>
+        <v>2140</v>
       </c>
       <c r="C4" t="n">
-        <v>7247</v>
+        <v>8478</v>
       </c>
       <c r="D4" t="n">
-        <v>8768</v>
+        <v>11703</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1676</v>
+        <v>1243</v>
       </c>
       <c r="C5" t="n">
-        <v>4002</v>
+        <v>6223</v>
       </c>
       <c r="D5" t="n">
-        <v>3215</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1052</v>
+        <v>729</v>
       </c>
       <c r="C6" t="n">
-        <v>1758</v>
+        <v>3884</v>
       </c>
       <c r="D6" t="n">
-        <v>987</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>265</v>
       </c>
       <c r="C7" t="n">
-        <v>1100</v>
+        <v>2329</v>
       </c>
       <c r="D7" t="n">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>623</v>
+        <v>1194</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6258</v>
+        <v>4417</v>
       </c>
       <c r="C2" t="n">
-        <v>4778</v>
+        <v>12124</v>
       </c>
       <c r="D2" t="n">
-        <v>17777</v>
+        <v>19581</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5263</v>
+        <v>3148</v>
       </c>
       <c r="C3" t="n">
-        <v>3545</v>
+        <v>4160</v>
       </c>
       <c r="D3" t="n">
-        <v>14916</v>
+        <v>17510</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4219</v>
+        <v>2474</v>
       </c>
       <c r="C4" t="n">
-        <v>6279</v>
+        <v>7301</v>
       </c>
       <c r="D4" t="n">
-        <v>9760</v>
+        <v>12621</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2119</v>
+        <v>1439</v>
       </c>
       <c r="C5" t="n">
-        <v>5608</v>
+        <v>7192</v>
       </c>
       <c r="D5" t="n">
-        <v>4076</v>
+        <v>5068</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1226</v>
+        <v>860</v>
       </c>
       <c r="C6" t="n">
-        <v>2816</v>
+        <v>4857</v>
       </c>
       <c r="D6" t="n">
-        <v>1337</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>620</v>
+        <v>391</v>
       </c>
       <c r="C7" t="n">
-        <v>1419</v>
+        <v>3006</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>839</v>
+        <v>1650</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>716</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2565,7 +2565,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3619</v>
+        <v>2617</v>
       </c>
       <c r="C2" t="n">
-        <v>2086</v>
+        <v>5755</v>
       </c>
       <c r="D2" t="n">
-        <v>12146</v>
+        <v>13683</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5323</v>
+        <v>3349</v>
       </c>
       <c r="C3" t="n">
-        <v>3868</v>
+        <v>6652</v>
       </c>
       <c r="D3" t="n">
-        <v>14877</v>
+        <v>17333</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4689</v>
+        <v>2708</v>
       </c>
       <c r="C4" t="n">
-        <v>5753</v>
+        <v>6854</v>
       </c>
       <c r="D4" t="n">
-        <v>10476</v>
+        <v>13314</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2225</v>
+        <v>1503</v>
       </c>
       <c r="C5" t="n">
-        <v>6521</v>
+        <v>8433</v>
       </c>
       <c r="D5" t="n">
-        <v>4512</v>
+        <v>5335</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1105</v>
+        <v>702</v>
       </c>
       <c r="C6" t="n">
-        <v>3592</v>
+        <v>5704</v>
       </c>
       <c r="D6" t="n">
-        <v>1313</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>1521</v>
+        <v>3076</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
-        <v>747</v>
+        <v>1186</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>48</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2862,7 +2862,7 @@
         <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6305</v>
+        <v>2822</v>
       </c>
       <c r="C2" t="n">
-        <v>2130</v>
+        <v>7743</v>
       </c>
       <c r="D2" t="n">
-        <v>10886</v>
+        <v>18331</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3904</v>
+        <v>2606</v>
       </c>
       <c r="C3" t="n">
-        <v>2646</v>
+        <v>5576</v>
       </c>
       <c r="D3" t="n">
-        <v>13460</v>
+        <v>15838</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4341</v>
+        <v>2583</v>
       </c>
       <c r="C4" t="n">
-        <v>4729</v>
+        <v>6684</v>
       </c>
       <c r="D4" t="n">
-        <v>10918</v>
+        <v>13526</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2894</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>6079</v>
+        <v>7575</v>
       </c>
       <c r="D5" t="n">
-        <v>5391</v>
+        <v>6321</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1434</v>
+        <v>910</v>
       </c>
       <c r="C6" t="n">
-        <v>4913</v>
+        <v>6890</v>
       </c>
       <c r="D6" t="n">
-        <v>1756</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>450</v>
+        <v>258</v>
       </c>
       <c r="C7" t="n">
-        <v>2443</v>
+        <v>4109</v>
       </c>
       <c r="D7" t="n">
-        <v>700</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>1064</v>
+        <v>1875</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>582</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4281</v>
+        <v>1861</v>
       </c>
       <c r="C2" t="n">
-        <v>2430</v>
+        <v>4867</v>
       </c>
       <c r="D2" t="n">
-        <v>8143</v>
+        <v>13693</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4162</v>
+        <v>2344</v>
       </c>
       <c r="C3" t="n">
-        <v>2206</v>
+        <v>5821</v>
       </c>
       <c r="D3" t="n">
-        <v>12376</v>
+        <v>15280</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3867</v>
+        <v>2382</v>
       </c>
       <c r="C4" t="n">
-        <v>3801</v>
+        <v>6301</v>
       </c>
       <c r="D4" t="n">
-        <v>11056</v>
+        <v>13533</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3207</v>
+        <v>1897</v>
       </c>
       <c r="C5" t="n">
-        <v>5641</v>
+        <v>7327</v>
       </c>
       <c r="D5" t="n">
-        <v>6020</v>
+        <v>7011</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1720</v>
+        <v>1057</v>
       </c>
       <c r="C6" t="n">
-        <v>5519</v>
+        <v>7453</v>
       </c>
       <c r="D6" t="n">
-        <v>2117</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>469</v>
+        <v>231</v>
       </c>
       <c r="C7" t="n">
-        <v>3311</v>
+        <v>4975</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>751</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>1442</v>
+        <v>2420</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>555</v>
+        <v>640</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6125</v>
+        <v>2751</v>
       </c>
       <c r="C2" t="n">
-        <v>6099</v>
+        <v>6366</v>
       </c>
       <c r="D2" t="n">
-        <v>8176</v>
+        <v>19461</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3532</v>
+        <v>1834</v>
       </c>
       <c r="C3" t="n">
-        <v>2053</v>
+        <v>4859</v>
       </c>
       <c r="D3" t="n">
-        <v>11087</v>
+        <v>14258</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3458</v>
+        <v>2079</v>
       </c>
       <c r="C4" t="n">
-        <v>2986</v>
+        <v>5971</v>
       </c>
       <c r="D4" t="n">
-        <v>10922</v>
+        <v>13226</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3174</v>
+        <v>1876</v>
       </c>
       <c r="C5" t="n">
-        <v>4711</v>
+        <v>6770</v>
       </c>
       <c r="D5" t="n">
-        <v>6504</v>
+        <v>7674</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2104</v>
+        <v>1238</v>
       </c>
       <c r="C6" t="n">
-        <v>5519</v>
+        <v>7344</v>
       </c>
       <c r="D6" t="n">
-        <v>2651</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>804</v>
+        <v>425</v>
       </c>
       <c r="C7" t="n">
-        <v>4250</v>
+        <v>5920</v>
       </c>
       <c r="D7" t="n">
-        <v>972</v>
+        <v>922</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="C8" t="n">
-        <v>2155</v>
+        <v>3270</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>881</v>
+        <v>1204</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3792,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6543</v>
+        <v>4385</v>
       </c>
       <c r="C2" t="n">
-        <v>3201</v>
+        <v>9844</v>
       </c>
       <c r="D2" t="n">
-        <v>5763</v>
+        <v>13275</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4243</v>
+        <v>1987</v>
       </c>
       <c r="C2" t="n">
-        <v>3269</v>
+        <v>3717</v>
       </c>
       <c r="D2" t="n">
-        <v>5952</v>
+        <v>14478</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4696</v>
+        <v>2473</v>
       </c>
       <c r="C3" t="n">
-        <v>3285</v>
+        <v>5619</v>
       </c>
       <c r="D3" t="n">
-        <v>11861</v>
+        <v>15666</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4701</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>4428</v>
+        <v>8361</v>
       </c>
       <c r="D4" t="n">
-        <v>11292</v>
+        <v>13649</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2120</v>
+        <v>1178</v>
       </c>
       <c r="C5" t="n">
-        <v>7366</v>
+        <v>10119</v>
       </c>
       <c r="D5" t="n">
-        <v>6080</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>742</v>
+        <v>392</v>
       </c>
       <c r="C6" t="n">
-        <v>5463</v>
+        <v>7169</v>
       </c>
       <c r="D6" t="n">
-        <v>2144</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="C7" t="n">
-        <v>2111</v>
+        <v>3204</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>863</v>
+        <v>1179</v>
       </c>
       <c r="D8" t="n">
-        <v>313</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6513</v>
+        <v>6663</v>
       </c>
       <c r="C2" t="n">
-        <v>2327</v>
+        <v>6224</v>
       </c>
       <c r="D2" t="n">
-        <v>12936</v>
+        <v>18117</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2779</v>
+        <v>1864</v>
       </c>
       <c r="C3" t="n">
-        <v>1638</v>
+        <v>4961</v>
       </c>
       <c r="D3" t="n">
-        <v>1653</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5638</v>
+        <v>4199</v>
       </c>
       <c r="C2" t="n">
-        <v>2772</v>
+        <v>8216</v>
       </c>
       <c r="D2" t="n">
-        <v>17014</v>
+        <v>24796</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3869</v>
+        <v>3496</v>
       </c>
       <c r="C3" t="n">
-        <v>1751</v>
+        <v>4894</v>
       </c>
       <c r="D3" t="n">
-        <v>3426</v>
+        <v>5219</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1241</v>
+        <v>844</v>
       </c>
       <c r="C4" t="n">
-        <v>1018</v>
+        <v>2951</v>
       </c>
       <c r="D4" t="n">
-        <v>1514</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4910,10 +4910,10 @@
         <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5472</v>
+        <v>5050</v>
       </c>
       <c r="C2" t="n">
-        <v>2928</v>
+        <v>5160</v>
       </c>
       <c r="D2" t="n">
-        <v>20877</v>
+        <v>39765</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3903</v>
+        <v>3165</v>
       </c>
       <c r="C3" t="n">
-        <v>2002</v>
+        <v>5785</v>
       </c>
       <c r="D3" t="n">
-        <v>5353</v>
+        <v>7975</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2198</v>
+        <v>1840</v>
       </c>
       <c r="C4" t="n">
-        <v>1419</v>
+        <v>3943</v>
       </c>
       <c r="D4" t="n">
-        <v>1820</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>568</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
-        <v>659</v>
+        <v>1709</v>
       </c>
       <c r="D5" t="n">
-        <v>1212</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>116</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5962</v>
+        <v>5195</v>
       </c>
       <c r="C2" t="n">
-        <v>3933</v>
+        <v>12493</v>
       </c>
       <c r="D2" t="n">
-        <v>24950</v>
+        <v>38693</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3830</v>
+        <v>3314</v>
       </c>
       <c r="C3" t="n">
-        <v>2161</v>
+        <v>4769</v>
       </c>
       <c r="D3" t="n">
-        <v>7335</v>
+        <v>12245</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2607</v>
+        <v>2102</v>
       </c>
       <c r="C4" t="n">
-        <v>1694</v>
+        <v>4795</v>
       </c>
       <c r="D4" t="n">
-        <v>2391</v>
+        <v>3319</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1150</v>
+        <v>916</v>
       </c>
       <c r="C5" t="n">
-        <v>1053</v>
+        <v>2831</v>
       </c>
       <c r="D5" t="n">
-        <v>1286</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>238</v>
       </c>
       <c r="C6" t="n">
-        <v>484</v>
+        <v>1002</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6573</v>
+        <v>5641</v>
       </c>
       <c r="C2" t="n">
-        <v>3991</v>
+        <v>9178</v>
       </c>
       <c r="D2" t="n">
-        <v>23352</v>
+        <v>29002</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3577</v>
+        <v>3054</v>
       </c>
       <c r="C3" t="n">
-        <v>2537</v>
+        <v>7082</v>
       </c>
       <c r="D3" t="n">
-        <v>9066</v>
+        <v>14490</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2023</v>
+        <v>1657</v>
       </c>
       <c r="C4" t="n">
-        <v>1609</v>
+        <v>3911</v>
       </c>
       <c r="D4" t="n">
-        <v>2855</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>986</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>1015</v>
+        <v>2775</v>
       </c>
       <c r="D5" t="n">
-        <v>1174</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>354</v>
+        <v>266</v>
       </c>
       <c r="C6" t="n">
-        <v>527</v>
+        <v>1283</v>
       </c>
       <c r="D6" t="n">
-        <v>753</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="C7" t="n">
-        <v>268</v>
+        <v>421</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5920</v>
+        <v>4986</v>
       </c>
       <c r="C2" t="n">
-        <v>5622</v>
+        <v>9043</v>
       </c>
       <c r="D2" t="n">
-        <v>19575</v>
+        <v>32816</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4263</v>
+        <v>3595</v>
       </c>
       <c r="C3" t="n">
-        <v>2935</v>
+        <v>7135</v>
       </c>
       <c r="D3" t="n">
-        <v>10898</v>
+        <v>15861</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2486</v>
+        <v>2058</v>
       </c>
       <c r="C4" t="n">
-        <v>2163</v>
+        <v>5717</v>
       </c>
       <c r="D4" t="n">
-        <v>4052</v>
+        <v>6171</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1350</v>
+        <v>1082</v>
       </c>
       <c r="C5" t="n">
-        <v>1358</v>
+        <v>3371</v>
       </c>
       <c r="D5" t="n">
-        <v>1493</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>637</v>
+        <v>477</v>
       </c>
       <c r="C6" t="n">
-        <v>810</v>
+        <v>2098</v>
       </c>
       <c r="D6" t="n">
-        <v>827</v>
+        <v>881</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>420</v>
+        <v>889</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" t="n">
-        <v>247</v>
+        <v>330</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
         <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5274</v>
+        <v>3661</v>
       </c>
       <c r="C2" t="n">
-        <v>8474</v>
+        <v>6263</v>
       </c>
       <c r="D2" t="n">
-        <v>21273</v>
+        <v>28291</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4206</v>
+        <v>3537</v>
       </c>
       <c r="C3" t="n">
-        <v>3859</v>
+        <v>7068</v>
       </c>
       <c r="D3" t="n">
-        <v>11553</v>
+        <v>17321</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2947</v>
+        <v>2386</v>
       </c>
       <c r="C4" t="n">
-        <v>2556</v>
+        <v>6374</v>
       </c>
       <c r="D4" t="n">
-        <v>5308</v>
+        <v>7691</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1695</v>
+        <v>1356</v>
       </c>
       <c r="C5" t="n">
-        <v>1801</v>
+        <v>4507</v>
       </c>
       <c r="D5" t="n">
-        <v>1924</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>701</v>
       </c>
       <c r="C6" t="n">
-        <v>1110</v>
+        <v>2734</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="C7" t="n">
-        <v>637</v>
+        <v>1504</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>340</v>
+        <v>600</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_29_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_29_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4747</v>
+        <v>846</v>
       </c>
       <c r="C2" t="n">
-        <v>5298</v>
+        <v>1653</v>
       </c>
       <c r="D2" t="n">
-        <v>35336</v>
+        <v>12038</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2976</v>
+        <v>1455</v>
       </c>
       <c r="C3" t="n">
-        <v>5862</v>
+        <v>4733</v>
       </c>
       <c r="D3" t="n">
-        <v>17708</v>
+        <v>12177</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2505</v>
+        <v>935</v>
       </c>
       <c r="C4" t="n">
-        <v>6526</v>
+        <v>7784</v>
       </c>
       <c r="D4" t="n">
-        <v>9121</v>
+        <v>4803</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1593</v>
+        <v>448</v>
       </c>
       <c r="C5" t="n">
-        <v>5327</v>
+        <v>5722</v>
       </c>
       <c r="D5" t="n">
-        <v>3312</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>908</v>
+        <v>217</v>
       </c>
       <c r="C6" t="n">
-        <v>3513</v>
+        <v>2243</v>
       </c>
       <c r="D6" t="n">
-        <v>1266</v>
+        <v>713</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>2081</v>
+        <v>756</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1001</v>
+        <v>351</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5305</v>
+        <v>576</v>
       </c>
       <c r="C2" t="n">
-        <v>7772</v>
+        <v>10150</v>
       </c>
       <c r="D2" t="n">
-        <v>28776</v>
+        <v>16145</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3040</v>
+        <v>981</v>
       </c>
       <c r="C3" t="n">
-        <v>4960</v>
+        <v>2675</v>
       </c>
       <c r="D3" t="n">
-        <v>18802</v>
+        <v>11394</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2337</v>
+        <v>1028</v>
       </c>
       <c r="C4" t="n">
-        <v>6084</v>
+        <v>5998</v>
       </c>
       <c r="D4" t="n">
-        <v>10075</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1738</v>
+        <v>594</v>
       </c>
       <c r="C5" t="n">
-        <v>5694</v>
+        <v>6746</v>
       </c>
       <c r="D5" t="n">
-        <v>4103</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1081</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>4263</v>
+        <v>3955</v>
       </c>
       <c r="D6" t="n">
-        <v>1531</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>547</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2663</v>
+        <v>1499</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>1445</v>
+        <v>536</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>639</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6012</v>
+        <v>299</v>
       </c>
       <c r="C2" t="n">
-        <v>7834</v>
+        <v>4173</v>
       </c>
       <c r="D2" t="n">
-        <v>24240</v>
+        <v>10894</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3185</v>
+        <v>829</v>
       </c>
       <c r="C3" t="n">
-        <v>5387</v>
+        <v>5493</v>
       </c>
       <c r="D3" t="n">
-        <v>18795</v>
+        <v>11692</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2226</v>
+        <v>1125</v>
       </c>
       <c r="C4" t="n">
-        <v>5435</v>
+        <v>5141</v>
       </c>
       <c r="D4" t="n">
-        <v>11025</v>
+        <v>6728</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1756</v>
+        <v>606</v>
       </c>
       <c r="C5" t="n">
-        <v>5678</v>
+        <v>7368</v>
       </c>
       <c r="D5" t="n">
-        <v>4741</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1215</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>4789</v>
+        <v>5049</v>
       </c>
       <c r="D6" t="n">
-        <v>1856</v>
+        <v>878</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>673</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3247</v>
+        <v>1403</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>307</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1883</v>
+        <v>506</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>924</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>218</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5548</v>
+        <v>545</v>
       </c>
       <c r="C2" t="n">
-        <v>5452</v>
+        <v>6646</v>
       </c>
       <c r="D2" t="n">
-        <v>20294</v>
+        <v>11574</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3877</v>
+        <v>498</v>
       </c>
       <c r="C3" t="n">
-        <v>8282</v>
+        <v>4223</v>
       </c>
       <c r="D3" t="n">
-        <v>20527</v>
+        <v>10747</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1622</v>
+        <v>883</v>
       </c>
       <c r="C4" t="n">
-        <v>8372</v>
+        <v>5272</v>
       </c>
       <c r="D4" t="n">
-        <v>10474</v>
+        <v>7493</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1122</v>
+        <v>751</v>
       </c>
       <c r="C5" t="n">
-        <v>4693</v>
+        <v>6152</v>
       </c>
       <c r="D5" t="n">
-        <v>3093</v>
+        <v>3086</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>621</v>
+        <v>366</v>
       </c>
       <c r="C6" t="n">
-        <v>3182</v>
+        <v>6208</v>
       </c>
       <c r="D6" t="n">
-        <v>814</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>1845</v>
+        <v>3073</v>
       </c>
       <c r="D7" t="n">
-        <v>472</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>905</v>
+        <v>889</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>405</v>
+        <v>344</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>67</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3370</v>
+        <v>354</v>
       </c>
       <c r="C2" t="n">
-        <v>2676</v>
+        <v>2960</v>
       </c>
       <c r="D2" t="n">
-        <v>14451</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3944</v>
+        <v>450</v>
       </c>
       <c r="C3" t="n">
-        <v>6394</v>
+        <v>4779</v>
       </c>
       <c r="D3" t="n">
-        <v>19510</v>
+        <v>10240</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2140</v>
+        <v>694</v>
       </c>
       <c r="C4" t="n">
-        <v>8478</v>
+        <v>4820</v>
       </c>
       <c r="D4" t="n">
-        <v>11703</v>
+        <v>7836</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1243</v>
+        <v>779</v>
       </c>
       <c r="C5" t="n">
-        <v>6223</v>
+        <v>5888</v>
       </c>
       <c r="D5" t="n">
-        <v>4009</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>449</v>
       </c>
       <c r="C6" t="n">
-        <v>3884</v>
+        <v>6442</v>
       </c>
       <c r="D6" t="n">
-        <v>1025</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>265</v>
+        <v>138</v>
       </c>
       <c r="C7" t="n">
-        <v>2329</v>
+        <v>4265</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1194</v>
+        <v>1416</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>373</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4417</v>
+        <v>608</v>
       </c>
       <c r="C2" t="n">
-        <v>12124</v>
+        <v>8758</v>
       </c>
       <c r="D2" t="n">
-        <v>19581</v>
+        <v>15364</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3148</v>
+        <v>345</v>
       </c>
       <c r="C3" t="n">
-        <v>4160</v>
+        <v>3455</v>
       </c>
       <c r="D3" t="n">
-        <v>17510</v>
+        <v>9464</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2474</v>
+        <v>517</v>
       </c>
       <c r="C4" t="n">
-        <v>7301</v>
+        <v>4699</v>
       </c>
       <c r="D4" t="n">
-        <v>12621</v>
+        <v>7990</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>691</v>
       </c>
       <c r="C5" t="n">
-        <v>7192</v>
+        <v>5319</v>
       </c>
       <c r="D5" t="n">
-        <v>5068</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>860</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>4857</v>
+        <v>6135</v>
       </c>
       <c r="D6" t="n">
-        <v>1441</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>391</v>
+        <v>226</v>
       </c>
       <c r="C7" t="n">
-        <v>3006</v>
+        <v>5243</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1650</v>
+        <v>2574</v>
       </c>
       <c r="D8" t="n">
-        <v>351</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>716</v>
+        <v>819</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2617</v>
+        <v>408</v>
       </c>
       <c r="C2" t="n">
-        <v>5755</v>
+        <v>4555</v>
       </c>
       <c r="D2" t="n">
-        <v>13683</v>
+        <v>11062</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>512</v>
       </c>
       <c r="C3" t="n">
-        <v>6652</v>
+        <v>5205</v>
       </c>
       <c r="D3" t="n">
-        <v>17333</v>
+        <v>10698</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2708</v>
+        <v>886</v>
       </c>
       <c r="C4" t="n">
-        <v>6854</v>
+        <v>6453</v>
       </c>
       <c r="D4" t="n">
-        <v>13314</v>
+        <v>8208</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1503</v>
+        <v>547</v>
       </c>
       <c r="C5" t="n">
-        <v>8433</v>
+        <v>8236</v>
       </c>
       <c r="D5" t="n">
-        <v>5335</v>
+        <v>3863</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>702</v>
+        <v>208</v>
       </c>
       <c r="C6" t="n">
-        <v>5704</v>
+        <v>6641</v>
       </c>
       <c r="D6" t="n">
-        <v>1398</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>68</v>
       </c>
       <c r="C7" t="n">
-        <v>3076</v>
+        <v>2522</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,10 +2730,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1186</v>
+        <v>802</v>
       </c>
       <c r="D8" t="n">
         <v>373</v>
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2822</v>
+        <v>217</v>
       </c>
       <c r="C2" t="n">
-        <v>7743</v>
+        <v>2296</v>
       </c>
       <c r="D2" t="n">
-        <v>18331</v>
+        <v>8626</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2606</v>
+        <v>397</v>
       </c>
       <c r="C3" t="n">
-        <v>5576</v>
+        <v>4303</v>
       </c>
       <c r="D3" t="n">
-        <v>15838</v>
+        <v>9983</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2583</v>
+        <v>596</v>
       </c>
       <c r="C4" t="n">
-        <v>6684</v>
+        <v>5461</v>
       </c>
       <c r="D4" t="n">
-        <v>13526</v>
+        <v>8039</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>498</v>
       </c>
       <c r="C5" t="n">
-        <v>7575</v>
+        <v>6553</v>
       </c>
       <c r="D5" t="n">
-        <v>6321</v>
+        <v>4010</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>910</v>
+        <v>201</v>
       </c>
       <c r="C6" t="n">
-        <v>6890</v>
+        <v>6101</v>
       </c>
       <c r="D6" t="n">
-        <v>1922</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>258</v>
+        <v>55</v>
       </c>
       <c r="C7" t="n">
-        <v>4109</v>
+        <v>3113</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1875</v>
+        <v>947</v>
       </c>
       <c r="D8" t="n">
-        <v>394</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>582</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1861</v>
+        <v>307</v>
       </c>
       <c r="C2" t="n">
-        <v>4867</v>
+        <v>10433</v>
       </c>
       <c r="D2" t="n">
-        <v>13693</v>
+        <v>10087</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2344</v>
+        <v>260</v>
       </c>
       <c r="C3" t="n">
-        <v>5821</v>
+        <v>2777</v>
       </c>
       <c r="D3" t="n">
-        <v>15280</v>
+        <v>9047</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>436</v>
       </c>
       <c r="C4" t="n">
-        <v>6301</v>
+        <v>4743</v>
       </c>
       <c r="D4" t="n">
-        <v>13533</v>
+        <v>8167</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1897</v>
+        <v>495</v>
       </c>
       <c r="C5" t="n">
-        <v>7327</v>
+        <v>5829</v>
       </c>
       <c r="D5" t="n">
-        <v>7011</v>
+        <v>4622</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1057</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>7453</v>
+        <v>6326</v>
       </c>
       <c r="D6" t="n">
-        <v>2274</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>231</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>4975</v>
+        <v>4605</v>
       </c>
       <c r="D7" t="n">
-        <v>751</v>
+        <v>719</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2420</v>
+        <v>1996</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>640</v>
+        <v>594</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2751</v>
+        <v>164</v>
       </c>
       <c r="C2" t="n">
-        <v>6366</v>
+        <v>16012</v>
       </c>
       <c r="D2" t="n">
-        <v>19461</v>
+        <v>11252</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1834</v>
+        <v>232</v>
       </c>
       <c r="C3" t="n">
-        <v>4859</v>
+        <v>5733</v>
       </c>
       <c r="D3" t="n">
-        <v>14258</v>
+        <v>8574</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2079</v>
+        <v>311</v>
       </c>
       <c r="C4" t="n">
-        <v>5971</v>
+        <v>3625</v>
       </c>
       <c r="D4" t="n">
-        <v>13226</v>
+        <v>7992</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1876</v>
+        <v>429</v>
       </c>
       <c r="C5" t="n">
-        <v>6770</v>
+        <v>5165</v>
       </c>
       <c r="D5" t="n">
-        <v>7674</v>
+        <v>5094</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1238</v>
+        <v>361</v>
       </c>
       <c r="C6" t="n">
-        <v>7344</v>
+        <v>6021</v>
       </c>
       <c r="D6" t="n">
-        <v>2836</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>425</v>
+        <v>173</v>
       </c>
       <c r="C7" t="n">
-        <v>5920</v>
+        <v>5412</v>
       </c>
       <c r="D7" t="n">
-        <v>922</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3270</v>
+        <v>3171</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1204</v>
+        <v>1198</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4385</v>
+        <v>3268</v>
       </c>
       <c r="C2" t="n">
-        <v>9844</v>
+        <v>9700</v>
       </c>
       <c r="D2" t="n">
-        <v>13275</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1987</v>
+        <v>274</v>
       </c>
       <c r="C2" t="n">
-        <v>3717</v>
+        <v>11682</v>
       </c>
       <c r="D2" t="n">
-        <v>14478</v>
+        <v>16723</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2473</v>
+        <v>171</v>
       </c>
       <c r="C3" t="n">
-        <v>5619</v>
+        <v>9138</v>
       </c>
       <c r="D3" t="n">
-        <v>15666</v>
+        <v>8444</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>240</v>
       </c>
       <c r="C4" t="n">
-        <v>8361</v>
+        <v>4486</v>
       </c>
       <c r="D4" t="n">
-        <v>13649</v>
+        <v>7761</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1178</v>
+        <v>353</v>
       </c>
       <c r="C5" t="n">
-        <v>10119</v>
+        <v>4362</v>
       </c>
       <c r="D5" t="n">
-        <v>6942</v>
+        <v>5384</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>392</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>7169</v>
+        <v>5535</v>
       </c>
       <c r="D6" t="n">
-        <v>2147</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>225</v>
       </c>
       <c r="C7" t="n">
-        <v>3204</v>
+        <v>5672</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>1179</v>
+        <v>4092</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>1959</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>680</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>218</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6663</v>
+        <v>2655</v>
       </c>
       <c r="C2" t="n">
-        <v>6224</v>
+        <v>11247</v>
       </c>
       <c r="D2" t="n">
-        <v>18117</v>
+        <v>7666</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1864</v>
+        <v>1081</v>
       </c>
       <c r="C3" t="n">
-        <v>4961</v>
+        <v>3830</v>
       </c>
       <c r="D3" t="n">
-        <v>2869</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4199</v>
+        <v>1833</v>
       </c>
       <c r="C2" t="n">
-        <v>8216</v>
+        <v>10055</v>
       </c>
       <c r="D2" t="n">
-        <v>24796</v>
+        <v>11292</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3496</v>
+        <v>1570</v>
       </c>
       <c r="C3" t="n">
-        <v>4894</v>
+        <v>7135</v>
       </c>
       <c r="D3" t="n">
-        <v>5219</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>844</v>
+        <v>526</v>
       </c>
       <c r="C4" t="n">
-        <v>2951</v>
+        <v>2437</v>
       </c>
       <c r="D4" t="n">
-        <v>1759</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5050</v>
+        <v>1345</v>
       </c>
       <c r="C2" t="n">
-        <v>5160</v>
+        <v>4633</v>
       </c>
       <c r="D2" t="n">
-        <v>39765</v>
+        <v>20972</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3165</v>
+        <v>1404</v>
       </c>
       <c r="C3" t="n">
-        <v>5785</v>
+        <v>7602</v>
       </c>
       <c r="D3" t="n">
-        <v>7975</v>
+        <v>3764</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1840</v>
+        <v>919</v>
       </c>
       <c r="C4" t="n">
-        <v>3943</v>
+        <v>5227</v>
       </c>
       <c r="D4" t="n">
-        <v>2369</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>400</v>
+        <v>270</v>
       </c>
       <c r="C5" t="n">
-        <v>1709</v>
+        <v>1508</v>
       </c>
       <c r="D5" t="n">
-        <v>1252</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5195</v>
+        <v>1765</v>
       </c>
       <c r="C2" t="n">
-        <v>12493</v>
+        <v>6394</v>
       </c>
       <c r="D2" t="n">
-        <v>38693</v>
+        <v>29589</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3314</v>
+        <v>1136</v>
       </c>
       <c r="C3" t="n">
-        <v>4769</v>
+        <v>5143</v>
       </c>
       <c r="D3" t="n">
-        <v>12245</v>
+        <v>6246</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2102</v>
+        <v>1005</v>
       </c>
       <c r="C4" t="n">
-        <v>4795</v>
+        <v>6486</v>
       </c>
       <c r="D4" t="n">
-        <v>3319</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>916</v>
+        <v>510</v>
       </c>
       <c r="C5" t="n">
-        <v>2831</v>
+        <v>3547</v>
       </c>
       <c r="D5" t="n">
-        <v>1394</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>238</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>1002</v>
+        <v>927</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5641</v>
+        <v>2089</v>
       </c>
       <c r="C2" t="n">
-        <v>9178</v>
+        <v>5195</v>
       </c>
       <c r="D2" t="n">
-        <v>29002</v>
+        <v>26299</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3054</v>
+        <v>1176</v>
       </c>
       <c r="C3" t="n">
-        <v>7082</v>
+        <v>5036</v>
       </c>
       <c r="D3" t="n">
-        <v>14490</v>
+        <v>9354</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1657</v>
+        <v>925</v>
       </c>
       <c r="C4" t="n">
-        <v>3911</v>
+        <v>5629</v>
       </c>
       <c r="D4" t="n">
-        <v>4232</v>
+        <v>2653</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>783</v>
+        <v>649</v>
       </c>
       <c r="C5" t="n">
-        <v>2775</v>
+        <v>4962</v>
       </c>
       <c r="D5" t="n">
-        <v>1353</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>1283</v>
+        <v>2249</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>421</v>
+        <v>609</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4986</v>
+        <v>1812</v>
       </c>
       <c r="C2" t="n">
-        <v>9043</v>
+        <v>5699</v>
       </c>
       <c r="D2" t="n">
-        <v>32816</v>
+        <v>21589</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3595</v>
+        <v>1296</v>
       </c>
       <c r="C3" t="n">
-        <v>7135</v>
+        <v>4474</v>
       </c>
       <c r="D3" t="n">
-        <v>15861</v>
+        <v>11150</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>890</v>
       </c>
       <c r="C4" t="n">
-        <v>5717</v>
+        <v>5210</v>
       </c>
       <c r="D4" t="n">
-        <v>6171</v>
+        <v>3730</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1082</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>3371</v>
+        <v>5185</v>
       </c>
       <c r="D5" t="n">
-        <v>1851</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>477</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>2098</v>
+        <v>3480</v>
       </c>
       <c r="D6" t="n">
-        <v>881</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>889</v>
+        <v>1380</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>330</v>
+        <v>439</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>284</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3661</v>
+        <v>1659</v>
       </c>
       <c r="C2" t="n">
-        <v>6263</v>
+        <v>3510</v>
       </c>
       <c r="D2" t="n">
-        <v>28291</v>
+        <v>16967</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3537</v>
+        <v>1652</v>
       </c>
       <c r="C3" t="n">
-        <v>7068</v>
+        <v>7094</v>
       </c>
       <c r="D3" t="n">
-        <v>17321</v>
+        <v>12046</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2386</v>
+        <v>639</v>
       </c>
       <c r="C4" t="n">
-        <v>6374</v>
+        <v>8228</v>
       </c>
       <c r="D4" t="n">
-        <v>7691</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1356</v>
+        <v>379</v>
       </c>
       <c r="C5" t="n">
-        <v>4507</v>
+        <v>3410</v>
       </c>
       <c r="D5" t="n">
-        <v>2582</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>701</v>
+        <v>167</v>
       </c>
       <c r="C6" t="n">
-        <v>2734</v>
+        <v>1352</v>
       </c>
       <c r="D6" t="n">
-        <v>1027</v>
+        <v>629</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>274</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1504</v>
+        <v>430</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>278</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>237</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
